--- a/data/bonds/Bonds10YR_Ready.xlsx
+++ b/data/bonds/Bonds10YR_Ready.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,16 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Z-Score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -450,6 +460,8 @@
       <c r="C2" t="n">
         <v>4.277725390625002</v>
       </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -461,6 +473,12 @@
       <c r="C3" t="n">
         <v>4.784476538461537</v>
       </c>
+      <c r="D3" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1695967213062147</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -472,6 +490,12 @@
       <c r="C4" t="n">
         <v>4.624893103448272</v>
       </c>
+      <c r="D4" t="n">
+        <v>-0.0334</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.2532742051403221</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -483,6 +507,12 @@
       <c r="C5" t="n">
         <v>3.6381393129771</v>
       </c>
+      <c r="D5" t="n">
+        <v>-0.2134</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.754372077163868</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -494,6 +524,12 @@
       <c r="C6" t="n">
         <v>3.240329501915708</v>
       </c>
+      <c r="D6" t="n">
+        <v>-0.1093</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.4645704745102506</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -505,6 +541,12 @@
       <c r="C7" t="n">
         <v>3.193982758620692</v>
       </c>
+      <c r="D7" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.2001021531644903</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -516,6 +558,12 @@
       <c r="C8" t="n">
         <v>2.759816923076925</v>
       </c>
+      <c r="D8" t="n">
+        <v>-0.1359</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.5386216044870635</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -527,6 +575,12 @@
       <c r="C9" t="n">
         <v>1.784344444444445</v>
       </c>
+      <c r="D9" t="n">
+        <v>-0.3535</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.144393254222195</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -538,6 +592,12 @@
       <c r="C10" t="n">
         <v>2.33465900383142</v>
       </c>
+      <c r="D10" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6982549762910557</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -549,6 +609,12 @@
       <c r="C11" t="n">
         <v>2.529037164750958</v>
       </c>
+      <c r="D11" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.07160424855494353</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -560,6 +626,12 @@
       <c r="C12" t="n">
         <v>2.131300000000001</v>
       </c>
+      <c r="D12" t="n">
+        <v>-0.1573</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.5981965737165296</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -571,6 +643,12 @@
       <c r="C13" t="n">
         <v>1.836771264367816</v>
       </c>
+      <c r="D13" t="n">
+        <v>-0.1382</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.5450245217406977</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -582,6 +660,12 @@
       <c r="C14" t="n">
         <v>2.326232692307693</v>
       </c>
+      <c r="D14" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5816105271922415</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -593,6 +677,12 @@
       <c r="C15" t="n">
         <v>2.907807662835251</v>
       </c>
+      <c r="D15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.535676555590083</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -604,6 +694,12 @@
       <c r="C16" t="n">
         <v>2.138363984674328</v>
       </c>
+      <c r="D16" t="n">
+        <v>-0.2646</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.8969065829838989</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -615,6 +711,12 @@
       <c r="C17" t="n">
         <v>0.8906187022900764</v>
       </c>
+      <c r="D17" t="n">
+        <v>-0.5835</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.784684979585615</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -626,6 +728,12 @@
       <c r="C18" t="n">
         <v>1.435065134099617</v>
       </c>
+      <c r="D18" t="n">
+        <v>0.6113</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.541491339824012</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -637,6 +745,12 @@
       <c r="C19" t="n">
         <v>2.950227692307694</v>
       </c>
+      <c r="D19" t="n">
+        <v>1.0558</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.778924696015491</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -648,6 +762,12 @@
       <c r="C20" t="n">
         <v>3.955332307692307</v>
       </c>
+      <c r="D20" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7881742055486143</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -658,6 +778,12 @@
       </c>
       <c r="C21" t="n">
         <v>4.20402375478927</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.01481315639227498</v>
       </c>
     </row>
   </sheetData>

--- a/data/bonds/Bonds10YR_Ready.xlsx
+++ b/data/bonds/Bonds10YR_Ready.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="USGG10YR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="GDBR10" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
         <v>2005</v>
       </c>
       <c r="C2" t="n">
-        <v>4.277725390625002</v>
+        <v>3.379525291828795</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -471,13 +471,13 @@
         <v>2006</v>
       </c>
       <c r="C3" t="n">
-        <v>4.784476538461537</v>
+        <v>3.782788461538462</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1185</v>
+        <v>0.1193</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1695967213062147</v>
+        <v>-0.0449638716431962</v>
       </c>
     </row>
     <row r="4">
@@ -488,13 +488,13 @@
         <v>2007</v>
       </c>
       <c r="C4" t="n">
-        <v>4.624893103448272</v>
+        <v>4.230214559386975</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0334</v>
+        <v>0.1183</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2532742051403221</v>
+        <v>-0.04573075993872647</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         <v>2008</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6381393129771</v>
+        <v>3.99570992366412</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2134</v>
+        <v>-0.0554</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.754372077163868</v>
+        <v>-0.1789392568723355</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         <v>2009</v>
       </c>
       <c r="C6" t="n">
-        <v>3.240329501915708</v>
+        <v>3.266425287356319</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1093</v>
+        <v>-0.1825</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4645704745102506</v>
+        <v>-0.2764107592342336</v>
       </c>
     </row>
     <row r="7">
@@ -539,13 +539,13 @@
         <v>2010</v>
       </c>
       <c r="C7" t="n">
-        <v>3.193982758620692</v>
+        <v>2.779409961685821</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0143</v>
+        <v>-0.1491</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2001021531644903</v>
+        <v>-0.2507966901635224</v>
       </c>
     </row>
     <row r="8">
@@ -556,13 +556,13 @@
         <v>2011</v>
       </c>
       <c r="C8" t="n">
-        <v>2.759816923076925</v>
+        <v>2.647430769230769</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1359</v>
+        <v>-0.0475</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5386216044870635</v>
+        <v>-0.1728808393376463</v>
       </c>
     </row>
     <row r="9">
@@ -573,13 +573,13 @@
         <v>2012</v>
       </c>
       <c r="C9" t="n">
-        <v>1.784344444444445</v>
+        <v>1.564509578544062</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3535</v>
+        <v>-0.409</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.144393254222195</v>
+        <v>-0.4501109581718412</v>
       </c>
     </row>
     <row r="10">
@@ -590,13 +590,13 @@
         <v>2013</v>
       </c>
       <c r="C10" t="n">
-        <v>2.33465900383142</v>
+        <v>1.627256704980841</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3084</v>
+        <v>0.0401</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6982549762910557</v>
+        <v>-0.1057014246491941</v>
       </c>
     </row>
     <row r="11">
@@ -607,13 +607,13 @@
         <v>2014</v>
       </c>
       <c r="C11" t="n">
-        <v>2.529037164750958</v>
+        <v>1.234693486590039</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0833</v>
+        <v>-0.2412</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07160424855494353</v>
+        <v>-0.3214271021818608</v>
       </c>
     </row>
     <row r="12">
@@ -624,13 +624,13 @@
         <v>2015</v>
       </c>
       <c r="C12" t="n">
-        <v>2.131300000000001</v>
+        <v>0.5369463601532564</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1573</v>
+        <v>-0.5651</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5981965737165296</v>
+        <v>-0.5698222211041174</v>
       </c>
     </row>
     <row r="13">
@@ -641,13 +641,13 @@
         <v>2016</v>
       </c>
       <c r="C13" t="n">
-        <v>1.836771264367816</v>
+        <v>0.1368544061302681</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1382</v>
+        <v>-0.7451</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5450245217406977</v>
+        <v>-0.7078621142995671</v>
       </c>
     </row>
     <row r="14">
@@ -658,13 +658,13 @@
         <v>2017</v>
       </c>
       <c r="C14" t="n">
-        <v>2.326232692307693</v>
+        <v>0.3745038461538464</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2665</v>
+        <v>1.7365</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5816105271922415</v>
+        <v>1.195247879888367</v>
       </c>
     </row>
     <row r="15">
@@ -675,13 +675,13 @@
         <v>2018</v>
       </c>
       <c r="C15" t="n">
-        <v>2.907807662835251</v>
+        <v>0.46316091954023</v>
       </c>
       <c r="D15" t="n">
-        <v>0.25</v>
+        <v>0.2367</v>
       </c>
       <c r="E15" t="n">
-        <v>0.535676555590083</v>
+        <v>0.04506881425205825</v>
       </c>
     </row>
     <row r="16">
@@ -692,13 +692,13 @@
         <v>2019</v>
       </c>
       <c r="C16" t="n">
-        <v>2.138363984674328</v>
+        <v>-0.2102653846153847</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2646</v>
+        <v>-1.454</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8969065829838989</v>
+        <v>-1.25150922700098</v>
       </c>
     </row>
     <row r="17">
@@ -709,13 +709,13 @@
         <v>2020</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8906187022900764</v>
+        <v>-0.4731679389312977</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5835</v>
+        <v>-1.2503</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.784684979585615</v>
+        <v>-1.095294081201463</v>
       </c>
     </row>
     <row r="18">
@@ -726,13 +726,13 @@
         <v>2021</v>
       </c>
       <c r="C18" t="n">
-        <v>1.435065134099617</v>
+        <v>-0.3087471264367818</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6113</v>
+        <v>0.3475</v>
       </c>
       <c r="E18" t="n">
-        <v>1.541491339824012</v>
+        <v>0.1300400373968129</v>
       </c>
     </row>
     <row r="19">
@@ -740,16 +740,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C19" t="n">
-        <v>2.950227692307694</v>
+        <v>2.460791505791506</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0558</v>
+        <v>1.0591</v>
       </c>
       <c r="E19" t="n">
-        <v>2.778924696015491</v>
+        <v>0.6757577484961574</v>
       </c>
     </row>
     <row r="20">
@@ -757,33 +757,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C20" t="n">
-        <v>3.955332307692307</v>
+        <v>2.341833976833973</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3407</v>
+        <v>-0.0483</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7881742055486143</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C21" t="n">
-        <v>4.20402375478927</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.0629</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.01481315639227498</v>
+        <v>-0.1734943499740705</v>
       </c>
     </row>
   </sheetData>
